--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B2" t="n">
-        <v>78105</v>
+        <v>79184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R2" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B3" t="n">
-        <v>79168</v>
+        <v>78121</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R3" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113440466</v>
       </c>
       <c r="B4" t="n">
-        <v>81846</v>
+        <v>81862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>79184</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R2" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>78121</v>
+        <v>79184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R3" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>79184</v>
+        <v>79196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113440466</v>
       </c>
       <c r="B4" t="n">
-        <v>81862</v>
+        <v>81874</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440423</v>
+        <v>113440466</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>81874</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751931</v>
+        <v>751757</v>
       </c>
       <c r="R2" t="n">
-        <v>7189645</v>
+        <v>7189737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440466</v>
+        <v>113440423</v>
       </c>
       <c r="B4" t="n">
-        <v>81874</v>
+        <v>78133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751757</v>
+        <v>751931</v>
       </c>
       <c r="R4" t="n">
-        <v>7189737</v>
+        <v>7189645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440466</v>
+        <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>81874</v>
+        <v>78155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751757</v>
+        <v>751931</v>
       </c>
       <c r="R2" t="n">
-        <v>7189737</v>
+        <v>7189645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440386</v>
+        <v>113440466</v>
       </c>
       <c r="B3" t="n">
-        <v>79196</v>
+        <v>81896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751762</v>
+        <v>751757</v>
       </c>
       <c r="R3" t="n">
-        <v>7189761</v>
+        <v>7189737</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B4" t="n">
-        <v>78133</v>
+        <v>79218</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R4" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B2" t="n">
-        <v>78155</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R2" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>113440466</v>
       </c>
       <c r="B3" t="n">
-        <v>81896</v>
+        <v>81900</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B4" t="n">
-        <v>79218</v>
+        <v>78158</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R4" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440386</v>
+        <v>113440466</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>81900</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751762</v>
+        <v>751757</v>
       </c>
       <c r="R2" t="n">
-        <v>7189761</v>
+        <v>7189737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440466</v>
+        <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>81900</v>
+        <v>79222</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751757</v>
+        <v>751762</v>
       </c>
       <c r="R3" t="n">
-        <v>7189737</v>
+        <v>7189761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440466</v>
+        <v>113440386</v>
       </c>
       <c r="B2" t="n">
-        <v>81900</v>
+        <v>79228</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751757</v>
+        <v>751762</v>
       </c>
       <c r="R2" t="n">
-        <v>7189737</v>
+        <v>7189761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B3" t="n">
-        <v>79222</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R3" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440423</v>
+        <v>113440466</v>
       </c>
       <c r="B4" t="n">
-        <v>78158</v>
+        <v>81906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751931</v>
+        <v>751757</v>
       </c>
       <c r="R4" t="n">
-        <v>7189645</v>
+        <v>7189737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R2" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>79228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R3" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>78171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>79228</v>
+        <v>79235</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113440466</v>
       </c>
       <c r="B4" t="n">
-        <v>81906</v>
+        <v>81913</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440423</v>
+        <v>113440466</v>
       </c>
       <c r="B2" t="n">
-        <v>78171</v>
+        <v>81916</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751931</v>
+        <v>751757</v>
       </c>
       <c r="R2" t="n">
-        <v>7189645</v>
+        <v>7189737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>79235</v>
+        <v>79237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440466</v>
+        <v>113440423</v>
       </c>
       <c r="B4" t="n">
-        <v>81913</v>
+        <v>78173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751757</v>
+        <v>751931</v>
       </c>
       <c r="R4" t="n">
-        <v>7189737</v>
+        <v>7189645</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440466</v>
+        <v>113440386</v>
       </c>
       <c r="B2" t="n">
-        <v>81916</v>
+        <v>79265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751757</v>
+        <v>751762</v>
       </c>
       <c r="R2" t="n">
-        <v>7189737</v>
+        <v>7189761</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B3" t="n">
-        <v>79237</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R3" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440423</v>
+        <v>113440466</v>
       </c>
       <c r="B4" t="n">
-        <v>78173</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751931</v>
+        <v>751757</v>
       </c>
       <c r="R4" t="n">
-        <v>7189645</v>
+        <v>7189737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B2" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R2" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440423</v>
+        <v>113440386</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>79265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751931</v>
+        <v>751762</v>
       </c>
       <c r="R3" t="n">
-        <v>7189645</v>
+        <v>7189761</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440423</v>
+        <v>113440466</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751931</v>
+        <v>751757</v>
       </c>
       <c r="R2" t="n">
-        <v>7189645</v>
+        <v>7189737</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440386</v>
+        <v>113440423</v>
       </c>
       <c r="B3" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751762</v>
+        <v>751931</v>
       </c>
       <c r="R3" t="n">
-        <v>7189761</v>
+        <v>7189645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440466</v>
+        <v>113440386</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751757</v>
+        <v>751762</v>
       </c>
       <c r="R4" t="n">
-        <v>7189737</v>
+        <v>7189761</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113440466</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,16 +780,11 @@
         <v>113440423</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -892,12 +882,7 @@
         <v>113440386</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41099-2023 artfynd.xlsx
+++ b/artfynd/A 41099-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440466</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440423</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113440386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>